--- a/辊筒上位机工程/通讯字表.xlsx
+++ b/辊筒上位机工程/通讯字表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通讯字" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通讯字表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="华文楷体"/>
       <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="楷体"/>
-      <b val="1"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -49,21 +38,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -71,37 +50,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -469,14 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="35.33" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9.25" customWidth="1" min="4" max="4"/>
-    <col width="66.25" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,416 +475,527 @@
           <t>手自动模式</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>40001</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>0为手动位(远程命令无效) 1为自动位(远程命令生效)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr"/>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>急停状态</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>40002</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>40002</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>0为释放 1为按下锁存(需复位解除)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>设备就绪</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>40003</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>40003</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>RunOK: 0未就绪 1就绪</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>辊筒正转运行</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>40004</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>40004</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>0停止 1正转中(Y10)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>辊筒反转运行</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>40005</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>40005</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0否 1反转中(Y11)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>阻挡升到位</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>40006</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>40006</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>磁开X6: 0未到位 1升到位</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>阻挡降到位</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>40007</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>40007</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>磁开X7: 0未到位 1降到位</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>气缸超时报警</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>40008</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>40008</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>0无 1有(锁存 需复位解除)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>位置检测1</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>40009</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>40009</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>进料段光电X3: 有料1 无料0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>位置检测2</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>40010</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>40010</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>中段光电X4: 有料1 无料0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>位置检测3</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>40011</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>40011</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>出料段光电X5: 有料1 无料0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>当前目标速度</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>40012</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>0.01Hz单位整数 PLC已缓存待发/已发的目标值</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40012</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>单位1RPM整数 PLC已缓存待发/已发的目标值</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>出向心跳</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>40013</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40013</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>PLC每1000ms自增1 上位机据此监测PLC存活</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>报警字</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>40014</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>位编码 bit0急停锁存 bit1气缸超时 bit2通讯断讯(自动恢复) 0=无报警</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>服务器写</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>辊筒正转启动</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>40021</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>40021</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>自动位写1启动正转 PLC置位后清0回执; 与停止/反转互斥</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>辊筒停止</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>40022</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>40022</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>写1停止辊筒(正反转均停) 执行后PLC清0回执</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>辊筒反转</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>40023</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>40023</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>自动位写1反转 与正转互斥 PLC置位后清0回执</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>阻挡升起</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>40024</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>40024</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>自动位写1 升线圈保持至升到位磁开; 与下降互斥</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>阻挡下降</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>40025</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>40025</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>自动位写1 降线圈保持至降到位磁开; 与升起互斥</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>报警复位</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>40026</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>40026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>写1解除急停/气缸超时锁存(须故障源已消除) 完成后清0回执</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr"/>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>变频器复位</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>40027</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>驱动器复位</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>40027</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>写1 触发Y12复位端子500ms脉冲(驱动器故障复位) 完成后清0回执</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>辊筒速度设定</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>40028</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>自动位下发 有效0~5000(0.01Hz 即0~50.00Hz) 变化时经RS485写入</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>40028</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>自动位下发 有效0~3000(单位1RPM) 变化时经RS485写入驱动器2001H</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>入向心跳</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>40029</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>40029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>上位机周期改变其值(建议自增); PLC超时3s判通讯丢失并切断输出</t>
         </is>

--- a/辊筒上位机工程/通讯字表.xlsx
+++ b/辊筒上位机工程/通讯字表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,11 +43,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,17 +55,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,11 +449,11 @@
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,7 +924,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>自动位写1 降线圈保持至降到位磁开; 与升起互斥</t>
+          <t>自动位写1 得电/失电切换(单电控: 失电弹簧降下)</t>
         </is>
       </c>
     </row>
